--- a/templates/出勤簿_template.xlsx
+++ b/templates/出勤簿_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanda\OneDrive\デスクトップ\加工場所\ﾀﾞﾝﾌﾟ運転手用勤怠システム開発\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kanda\OneDrive\デスクトップ\加工場所\ﾀﾞﾝﾌﾟ運転手用勤怠システム開発\dump-attendance\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF901C75-A019-4E59-9213-418E2BEE0B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23428145-E5B3-4C95-A1B7-6971F2F23852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" xWindow="780" yWindow="750" windowWidth="23385" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="出勤簿" sheetId="1" r:id="rId1"/>
@@ -939,7 +939,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -1116,11 +1116,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1295,29 +1313,8 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1337,6 +1334,12 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1347,6 +1350,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="55" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1369,6 +1384,15 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1732,23 +1756,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:30" ht="33.75" customHeight="1">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
-      <c r="O1" s="67"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
+      <c r="O1" s="60"/>
       <c r="P1" s="1"/>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
@@ -1765,12 +1789,12 @@
       <c r="K2" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="72">
+      <c r="L2" s="67">
         <v>46033</v>
       </c>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="72"/>
+      <c r="M2" s="67"/>
+      <c r="N2" s="67"/>
+      <c r="O2" s="67"/>
       <c r="P2" s="23"/>
       <c r="Q2" s="23"/>
       <c r="R2" s="23"/>
@@ -1814,13 +1838,13 @@
       <c r="K4" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="71" t="str">
+      <c r="L4" s="66" t="str">
         <f>+YEAR(L2)&amp;"/"&amp;MONTH(L2+30)&amp;"/10"</f>
         <v>2026/2/10</v>
       </c>
-      <c r="M4" s="71"/>
-      <c r="N4" s="71"/>
-      <c r="O4" s="71"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="66"/>
+      <c r="O4" s="66"/>
       <c r="P4" s="23"/>
       <c r="Q4" s="23"/>
       <c r="R4" s="23"/>
@@ -1864,19 +1888,19 @@
     <row r="6" spans="1:30" ht="21" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
-      <c r="D6" s="62" t="s">
+      <c r="D6" s="64" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="73" t="s">
+      <c r="E6" s="65"/>
+      <c r="F6" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="G6" s="74"/>
+      <c r="G6" s="69"/>
       <c r="H6" s="22"/>
       <c r="L6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M6" s="68" t="str">
+      <c r="M6" s="61" t="str">
         <f>L4</f>
         <v>2026/2/10</v>
       </c>
@@ -1906,7 +1930,7 @@
       <c r="L7" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="62" t="s">
         <v>37</v>
       </c>
       <c r="N7" s="56"/>
@@ -1937,7 +1961,7 @@
       <c r="L8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M8" s="69" t="s">
+      <c r="M8" s="62" t="s">
         <v>38</v>
       </c>
       <c r="N8" s="56"/>
@@ -1980,7 +2004,7 @@
       <c r="AB9" s="2"/>
     </row>
     <row r="10" spans="1:30" ht="34.5" customHeight="1">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B10" s="56"/>
@@ -4734,11 +4758,11 @@
         <v>23</v>
       </c>
       <c r="F48" s="2"/>
-      <c r="G48" s="65" t="s">
+      <c r="G48" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="H48" s="65"/>
-      <c r="I48" s="65"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="58"/>
       <c r="J48" s="45">
         <f>SUM(J11:J46)-J52</f>
         <v>1.354166666666667</v>
@@ -4781,9 +4805,9 @@
       <c r="I49" s="2"/>
       <c r="J49" s="2"/>
       <c r="K49" s="2"/>
-      <c r="L49" s="57"/>
-      <c r="M49" s="57"/>
-      <c r="N49" s="57"/>
+      <c r="L49" s="82"/>
+      <c r="M49" s="82"/>
+      <c r="N49" s="82"/>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
       <c r="U49" s="2"/>
@@ -4806,19 +4830,19 @@
         <f>COUNTIFS(C11:C46,"有給")+COUNTIFS(C11:C46,"午前有給")*0.5+COUNTIFS(C11:C46,"午後有給")*0.5</f>
         <v>0</v>
       </c>
-      <c r="G50" s="65" t="s">
+      <c r="G50" s="58" t="s">
         <v>75</v>
       </c>
-      <c r="H50" s="65"/>
-      <c r="I50" s="65"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
       <c r="J50" s="46">
         <f>SUMIF(C11:C46,"法定休日出勤",I11:I46)</f>
         <v>0</v>
       </c>
       <c r="K50" s="2"/>
-      <c r="L50" s="58"/>
-      <c r="M50" s="58"/>
-      <c r="N50" s="58"/>
+      <c r="L50" s="57"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="57"/>
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
       <c r="U50" s="2"/>
@@ -4842,19 +4866,19 @@
         <v>7.666666666666667</v>
       </c>
       <c r="F51" s="2"/>
-      <c r="G51" s="65" t="s">
+      <c r="G51" s="58" t="s">
         <v>76</v>
       </c>
-      <c r="H51" s="65"/>
-      <c r="I51" s="65"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
       <c r="J51" s="46">
         <f>SUMIF(C11:C46,"所定休日出勤",I11:I46)</f>
         <v>0</v>
       </c>
       <c r="K51" s="2"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="81"/>
+      <c r="N51" s="81"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
       <c r="U51" s="2"/>
@@ -4878,11 +4902,11 @@
         <v>7.666666666666667</v>
       </c>
       <c r="F52" s="2"/>
-      <c r="G52" s="65" t="s">
+      <c r="G52" s="58" t="s">
         <v>77</v>
       </c>
-      <c r="H52" s="65"/>
-      <c r="I52" s="65"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="58"/>
       <c r="J52" s="46">
         <f>+J50+J51</f>
         <v>0</v>
@@ -4913,11 +4937,12 @@
       <c r="L53" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="M53" s="62" t="s">
+      <c r="M53" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="N53" s="63"/>
-      <c r="O53" s="64"/>
+      <c r="N53" s="73"/>
+      <c r="O53" s="65"/>
+      <c r="P53" s="83"/>
       <c r="U53" s="2"/>
       <c r="V53" s="2"/>
     </row>
@@ -4935,12 +4960,13 @@
       <c r="L54" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="M54" s="59">
+      <c r="M54" s="70">
         <f>+L4+365*4+366+1</f>
         <v>47890</v>
       </c>
-      <c r="N54" s="60"/>
-      <c r="O54" s="61"/>
+      <c r="N54" s="71"/>
+      <c r="O54" s="72"/>
+      <c r="P54" s="83"/>
       <c r="U54" s="2"/>
       <c r="V54" s="2"/>
       <c r="AA54" s="2"/>
@@ -4963,7 +4989,7 @@
       <c r="N55" s="2"/>
       <c r="O55" s="29" t="str" cm="1">
         <f t="array" aca="1" ref="O55" ca="1">+CELL("filename")</f>
-        <v>\\192.168.1.101\data\02_工場事務\勤怠関係\工場勤怠表2026年\ﾀﾞﾝﾌﾟ運転手勤怠2026年\池田\[池田出勤簿_260210(再改定).xlsx]出勤簿</v>
+        <v>C:\Users\kanda\OneDrive\デスクトップ\加工場所\ﾀﾞﾝﾌﾟ運転手用勤怠システム開発\dump-attendance\templates\[出勤簿_template.xlsx]出勤簿</v>
       </c>
       <c r="U55" s="2"/>
       <c r="V55" s="2"/>
@@ -29699,13 +29725,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C48:D48"/>
-    <mergeCell ref="C51:D51"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="M49:M50"/>
-    <mergeCell ref="C49:D49"/>
-    <mergeCell ref="C50:D50"/>
-    <mergeCell ref="G48:I48"/>
+    <mergeCell ref="C52:D52"/>
+    <mergeCell ref="N49:N50"/>
+    <mergeCell ref="M54:O54"/>
+    <mergeCell ref="M53:O53"/>
+    <mergeCell ref="G52:I52"/>
+    <mergeCell ref="G51:I51"/>
+    <mergeCell ref="G50:I50"/>
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="M7:N7"/>
@@ -29715,13 +29741,13 @@
     <mergeCell ref="L4:O4"/>
     <mergeCell ref="L2:O2"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="C52:D52"/>
-    <mergeCell ref="N49:N50"/>
-    <mergeCell ref="M54:O54"/>
-    <mergeCell ref="M53:O53"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="G51:I51"/>
-    <mergeCell ref="G50:I50"/>
+    <mergeCell ref="C48:D48"/>
+    <mergeCell ref="C51:D51"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="M49:M50"/>
+    <mergeCell ref="C49:D49"/>
+    <mergeCell ref="C50:D50"/>
+    <mergeCell ref="G48:I48"/>
   </mergeCells>
   <phoneticPr fontId="6"/>
   <conditionalFormatting sqref="A11:B46">
@@ -29769,30 +29795,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A1" s="66"/>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="G1" s="67"/>
-      <c r="H1" s="67"/>
-      <c r="I1" s="67"/>
-      <c r="J1" s="67"/>
-      <c r="K1" s="67"/>
-      <c r="L1" s="67"/>
-      <c r="M1" s="67"/>
-      <c r="N1" s="67"/>
+      <c r="A1" s="59"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
+      <c r="K1" s="60"/>
+      <c r="L1" s="60"/>
+      <c r="M1" s="60"/>
+      <c r="N1" s="60"/>
     </row>
     <row r="2" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A2" s="75">
+      <c r="A2" s="74">
         <f>出勤簿!$L$2</f>
         <v>46033</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
       <c r="F2" s="56"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -29830,8 +29856,8 @@
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="16"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="67"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="60"/>
       <c r="M4" s="16"/>
       <c r="N4" s="2"/>
     </row>
@@ -29846,8 +29872,8 @@
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="16"/>
-      <c r="K5" s="78"/>
-      <c r="L5" s="67"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="60"/>
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
@@ -29862,8 +29888,8 @@
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
       <c r="J6" s="16"/>
-      <c r="K6" s="78"/>
-      <c r="L6" s="67"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="60"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
     </row>
@@ -29884,7 +29910,7 @@
       <c r="N7" s="2"/>
     </row>
     <row r="8" spans="1:14" ht="18.75" customHeight="1">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="63" t="s">
         <v>0</v>
       </c>
       <c r="B8" s="56"/>
@@ -63455,16 +63481,16 @@
       <c r="H2" s="43"/>
     </row>
     <row r="3" spans="1:8" ht="15.75">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="78" t="s">
         <v>66</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="49" t="s">
@@ -63502,13 +63528,13 @@
       <c r="B12" s="51" t="s">
         <v>73</v>
       </c>
-      <c r="C12" s="81" t="s">
+      <c r="C12" s="80" t="s">
         <v>74</v>
       </c>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="52" t="s">
@@ -63517,13 +63543,13 @@
       <c r="B13" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="81" t="s">
+      <c r="C13" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="80"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="80"/>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="52" t="s">
@@ -63532,13 +63558,13 @@
       <c r="B14" s="52" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="81" t="s">
+      <c r="C14" s="80" t="s">
         <v>71</v>
       </c>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
+      <c r="D14" s="80"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="48" t="s">
